--- a/data/trans_orig/P43D-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P43D-Provincia-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19175</t>
+          <t>19735</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38947</t>
+          <t>39723</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19175</t>
+          <t>19735</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38947</t>
+          <t>39723</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39977</t>
+          <t>38398</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63261</t>
+          <t>61990</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39977</t>
+          <t>38398</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63261</t>
+          <t>61990</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>42,39%</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25017</t>
+          <t>25416</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47050</t>
+          <t>47792</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25017</t>
+          <t>25416</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47050</t>
+          <t>47792</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,68%</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23421</t>
+          <t>21771</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44188</t>
+          <t>43683</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23421</t>
+          <t>21771</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44188</t>
+          <t>43683</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,87%</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64668</t>
+          <t>64064</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>93517</t>
+          <t>92705</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>64668</t>
+          <t>64064</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93517</t>
+          <t>92705</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62442</t>
+          <t>61742</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91971</t>
+          <t>91089</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62442</t>
+          <t>61742</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91971</t>
+          <t>91089</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,76%</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65010</t>
+          <t>64312</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>92474</t>
+          <t>93195</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65010</t>
+          <t>64312</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92474</t>
+          <t>93195</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27786</t>
+          <t>27836</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51530</t>
+          <t>49670</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27786</t>
+          <t>27836</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51530</t>
+          <t>49670</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33782</t>
+          <t>33175</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>57138</t>
+          <t>56778</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33782</t>
+          <t>33175</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57138</t>
+          <t>56778</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,19%</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>56617</t>
+          <t>58145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>82407</t>
+          <t>83415</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>56617</t>
+          <t>58145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>82407</t>
+          <t>83415</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1589,12 +1589,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>44,35%</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30215</t>
+          <t>30882</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53064</t>
+          <t>52887</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1632,12 +1632,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30215</t>
+          <t>30882</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53064</t>
+          <t>52887</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -1695,12 +1695,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24355</t>
+          <t>24477</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46014</t>
+          <t>45221</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24355</t>
+          <t>24477</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46014</t>
+          <t>45221</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,04%</t>
         </is>
       </c>
     </row>
@@ -1855,12 +1855,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43873</t>
+          <t>44639</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>70040</t>
+          <t>69849</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43873</t>
+          <t>44639</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>70040</t>
+          <t>69849</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,55%</t>
         </is>
       </c>
     </row>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43179</t>
+          <t>43590</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66682</t>
+          <t>67007</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43179</t>
+          <t>43590</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66682</t>
+          <t>67007</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1983,12 +1983,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -2011,12 +2011,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>46210</t>
+          <t>45627</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>70713</t>
+          <t>70755</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46210</t>
+          <t>45627</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>70713</t>
+          <t>70755</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,98%</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28593</t>
+          <t>28693</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50846</t>
+          <t>50613</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28593</t>
+          <t>28693</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50846</t>
+          <t>50613</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,31%</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8608</t>
+          <t>9099</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23293</t>
+          <t>23339</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8608</t>
+          <t>9099</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23293</t>
+          <t>23339</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20464</t>
+          <t>19964</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38806</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20464</t>
+          <t>19964</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38806</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>44,94%</t>
         </is>
       </c>
     </row>
@@ -2405,12 +2405,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11596</t>
+          <t>12095</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27799</t>
+          <t>27987</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11596</t>
+          <t>12095</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27799</t>
+          <t>27987</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,0%</t>
         </is>
       </c>
     </row>
@@ -2483,12 +2483,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14009</t>
+          <t>14137</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>31185</t>
+          <t>30702</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>14009</t>
+          <t>14137</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>31185</t>
+          <t>30702</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,2%</t>
         </is>
       </c>
     </row>
@@ -2643,12 +2643,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>28972</t>
+          <t>29114</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>50034</t>
+          <t>49967</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28972</t>
+          <t>29114</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>50034</t>
+          <t>49967</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,23%</t>
         </is>
       </c>
     </row>
@@ -2721,12 +2721,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>25199</t>
+          <t>24802</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>45598</t>
+          <t>44165</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>25199</t>
+          <t>24802</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>45598</t>
+          <t>44165</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>34,68%</t>
         </is>
       </c>
     </row>
@@ -2799,12 +2799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19980</t>
+          <t>21680</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>40063</t>
+          <t>41745</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2834,12 +2834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>19980</t>
+          <t>21680</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>40063</t>
+          <t>41745</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>32,78%</t>
         </is>
       </c>
     </row>
@@ -2877,12 +2877,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>16157</t>
+          <t>16985</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>34479</t>
+          <t>34738</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2912,12 +2912,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>16157</t>
+          <t>16985</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>34479</t>
+          <t>34738</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -3037,12 +3037,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>75766</t>
+          <t>78329</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>110754</t>
+          <t>112276</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>75766</t>
+          <t>78329</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>110754</t>
+          <t>112276</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>99378</t>
+          <t>99471</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>135929</t>
+          <t>133746</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>99378</t>
+          <t>99471</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>135929</t>
+          <t>133746</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,47%</t>
         </is>
       </c>
     </row>
@@ -3193,12 +3193,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>92437</t>
+          <t>91551</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>128618</t>
+          <t>127846</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -3228,12 +3228,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>92437</t>
+          <t>91551</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>128618</t>
+          <t>127846</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>31,99%</t>
         </is>
       </c>
     </row>
@@ -3271,12 +3271,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>63124</t>
+          <t>65725</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>96625</t>
+          <t>98365</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>63124</t>
+          <t>65725</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>96625</t>
+          <t>98365</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -3431,12 +3431,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>52827</t>
+          <t>53104</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>82910</t>
+          <t>83130</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -3446,12 +3446,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>52827</t>
+          <t>53104</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>82910</t>
+          <t>83130</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -3509,12 +3509,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>107435</t>
+          <t>105753</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>143222</t>
+          <t>142495</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>107435</t>
+          <t>105753</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>143222</t>
+          <t>142495</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,14%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>84475</t>
+          <t>85175</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>118209</t>
+          <t>121354</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>84475</t>
+          <t>85175</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>118209</t>
+          <t>121354</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>34,19%</t>
         </is>
       </c>
     </row>
@@ -3665,12 +3665,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>49990</t>
+          <t>48394</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>79171</t>
+          <t>79319</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>49990</t>
+          <t>48394</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>79171</t>
+          <t>79319</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>388118</t>
+          <t>383297</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>459721</t>
+          <t>456740</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>388118</t>
+          <t>383297</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>459721</t>
+          <t>456740</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>
@@ -3903,12 +3903,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>515341</t>
+          <t>512955</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>596654</t>
+          <t>594393</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>515341</t>
+          <t>512955</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>596654</t>
+          <t>594393</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -3981,12 +3981,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>430680</t>
+          <t>434950</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>505487</t>
+          <t>510469</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>430680</t>
+          <t>434950</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>505487</t>
+          <t>510469</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -4059,12 +4059,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>298182</t>
+          <t>299895</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>364568</t>
+          <t>363947</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -4094,12 +4094,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>298182</t>
+          <t>299895</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>364568</t>
+          <t>363947</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -4109,12 +4109,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26078</t>
+          <t>26135</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50531</t>
+          <t>49949</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26078</t>
+          <t>26135</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50531</t>
+          <t>49949</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -4472,12 +4472,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33120</t>
+          <t>34239</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60153</t>
+          <t>60481</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4487,12 +4487,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33120</t>
+          <t>34239</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60153</t>
+          <t>60481</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -4550,12 +4550,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64554</t>
+          <t>63144</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>93330</t>
+          <t>93005</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4585,12 +4585,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>64554</t>
+          <t>63144</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>93330</t>
+          <t>93005</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4600,12 +4600,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,32%</t>
         </is>
       </c>
     </row>
@@ -4628,12 +4628,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29842</t>
+          <t>29413</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53298</t>
+          <t>53863</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29842</t>
+          <t>29413</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53298</t>
+          <t>53863</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,82%</t>
         </is>
       </c>
     </row>
@@ -4788,12 +4788,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58534</t>
+          <t>55995</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>89569</t>
+          <t>88806</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>58534</t>
+          <t>55995</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>89569</t>
+          <t>88806</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -4866,12 +4866,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>101648</t>
+          <t>102197</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>139542</t>
+          <t>139786</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4881,12 +4881,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>101648</t>
+          <t>102197</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>139542</t>
+          <t>139786</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4916,12 +4916,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,86%</t>
         </is>
       </c>
     </row>
@@ -4944,12 +4944,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93257</t>
+          <t>93191</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>129589</t>
+          <t>130338</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4959,12 +4959,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4979,12 +4979,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93257</t>
+          <t>93191</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>129589</t>
+          <t>130338</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4994,12 +4994,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -5022,12 +5022,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>61140</t>
+          <t>59868</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>92300</t>
+          <t>93017</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5057,12 +5057,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>61140</t>
+          <t>59868</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>92300</t>
+          <t>93017</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,52%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25703</t>
+          <t>25570</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49051</t>
+          <t>47688</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25703</t>
+          <t>25570</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49051</t>
+          <t>47688</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -5260,12 +5260,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>66859</t>
+          <t>65734</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>93593</t>
+          <t>93746</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5275,12 +5275,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>66859</t>
+          <t>65734</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>93593</t>
+          <t>93746</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,68%</t>
         </is>
       </c>
     </row>
@@ -5338,12 +5338,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33488</t>
+          <t>32898</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57372</t>
+          <t>57114</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33488</t>
+          <t>32898</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57372</t>
+          <t>57114</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5388,12 +5388,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23135</t>
+          <t>23416</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45433</t>
+          <t>46820</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5451,12 +5451,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23135</t>
+          <t>23416</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45433</t>
+          <t>46820</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>24,31%</t>
         </is>
       </c>
     </row>
@@ -5576,12 +5576,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35367</t>
+          <t>35036</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>60436</t>
+          <t>59591</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35367</t>
+          <t>35036</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60436</t>
+          <t>59591</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -5654,12 +5654,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>71775</t>
+          <t>71584</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>104459</t>
+          <t>102304</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71775</t>
+          <t>71584</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>104459</t>
+          <t>102304</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>39,45%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>57477</t>
+          <t>58377</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>89896</t>
+          <t>88245</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>57477</t>
+          <t>58377</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>89896</t>
+          <t>88245</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>
@@ -5810,12 +5810,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42394</t>
+          <t>43826</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70088</t>
+          <t>69683</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5845,12 +5845,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42394</t>
+          <t>43826</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>70088</t>
+          <t>69683</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5860,12 +5860,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,87%</t>
         </is>
       </c>
     </row>
@@ -5970,12 +5970,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11233</t>
+          <t>11314</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27771</t>
+          <t>28731</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5985,12 +5985,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6005,12 +6005,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11233</t>
+          <t>11314</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27771</t>
+          <t>28731</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>21,02%</t>
         </is>
       </c>
     </row>
@@ -6048,12 +6048,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>40170</t>
+          <t>40174</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>62854</t>
+          <t>62365</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6063,12 +6063,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>40170</t>
+          <t>40174</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>62854</t>
+          <t>62365</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6098,12 +6098,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>45,63%</t>
         </is>
       </c>
     </row>
@@ -6126,12 +6126,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31951</t>
+          <t>32610</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>54418</t>
+          <t>55996</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6141,12 +6141,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>31951</t>
+          <t>32610</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>54418</t>
+          <t>55996</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6176,12 +6176,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>40,97%</t>
         </is>
       </c>
     </row>
@@ -6204,12 +6204,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>15161</t>
+          <t>15363</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>33237</t>
+          <t>34384</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6219,12 +6219,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>15161</t>
+          <t>15363</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>33237</t>
+          <t>34384</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6254,12 +6254,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>25,16%</t>
         </is>
       </c>
     </row>
@@ -6364,12 +6364,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>30778</t>
+          <t>29582</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>52626</t>
+          <t>51901</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>30778</t>
+          <t>29582</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>52626</t>
+          <t>51901</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6414,12 +6414,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,01%</t>
         </is>
       </c>
     </row>
@@ -6442,12 +6442,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>46774</t>
+          <t>45834</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>70624</t>
+          <t>70443</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>46774</t>
+          <t>45834</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>70624</t>
+          <t>70443</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,16%</t>
         </is>
       </c>
     </row>
@@ -6520,12 +6520,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>24510</t>
+          <t>23936</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>44711</t>
+          <t>46142</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -6535,12 +6535,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -6555,12 +6555,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>24510</t>
+          <t>23936</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>44711</t>
+          <t>46142</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -6598,12 +6598,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12677</t>
+          <t>12262</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>29068</t>
+          <t>28847</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -6613,12 +6613,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -6633,12 +6633,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>12677</t>
+          <t>12262</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>29068</t>
+          <t>28847</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -6648,12 +6648,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>75397</t>
+          <t>76048</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>111021</t>
+          <t>112433</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>75397</t>
+          <t>76048</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>111021</t>
+          <t>112433</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -6808,12 +6808,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,65%</t>
         </is>
       </c>
     </row>
@@ -6836,12 +6836,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>129941</t>
+          <t>131533</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>172163</t>
+          <t>172234</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>129941</t>
+          <t>131533</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>172163</t>
+          <t>172234</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,29%</t>
         </is>
       </c>
     </row>
@@ -6914,12 +6914,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>96225</t>
+          <t>94123</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>136237</t>
+          <t>133182</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>96225</t>
+          <t>94123</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>136237</t>
+          <t>133182</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -6992,12 +6992,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>63492</t>
+          <t>65281</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>98582</t>
+          <t>100066</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>63492</t>
+          <t>65281</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>98582</t>
+          <t>100066</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -7152,12 +7152,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>85240</t>
+          <t>86285</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>123436</t>
+          <t>124150</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -7167,12 +7167,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>85240</t>
+          <t>86285</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>123436</t>
+          <t>124150</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -7202,12 +7202,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -7230,12 +7230,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>176159</t>
+          <t>176432</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>222895</t>
+          <t>223186</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -7245,12 +7245,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>176159</t>
+          <t>176432</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>222895</t>
+          <t>223186</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -7280,12 +7280,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,09%</t>
         </is>
       </c>
     </row>
@@ -7308,12 +7308,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>122407</t>
+          <t>122477</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>165207</t>
+          <t>162922</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>122407</t>
+          <t>122477</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>165207</t>
+          <t>162922</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -7358,12 +7358,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,72%</t>
         </is>
       </c>
     </row>
@@ -7386,12 +7386,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>67756</t>
+          <t>68789</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>105864</t>
+          <t>103329</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>67756</t>
+          <t>68789</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>105864</t>
+          <t>103329</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -7546,12 +7546,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>406009</t>
+          <t>409046</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>485969</t>
+          <t>488812</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>406009</t>
+          <t>409046</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>485969</t>
+          <t>488812</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -7624,12 +7624,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>744514</t>
+          <t>740642</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>840524</t>
+          <t>837069</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -7659,12 +7659,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>744514</t>
+          <t>740642</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>840524</t>
+          <t>837069</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -7674,12 +7674,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,55%</t>
         </is>
       </c>
     </row>
@@ -7702,12 +7702,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>592669</t>
+          <t>597123</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>681823</t>
+          <t>681811</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>592669</t>
+          <t>597123</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>681823</t>
+          <t>681811</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -7780,12 +7780,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>380150</t>
+          <t>378136</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>456811</t>
+          <t>454248</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -7795,12 +7795,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -7815,12 +7815,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>380150</t>
+          <t>378136</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>456811</t>
+          <t>454248</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -8115,12 +8115,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25595</t>
+          <t>24751</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47421</t>
+          <t>49440</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25595</t>
+          <t>24751</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47421</t>
+          <t>49440</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>24,38%</t>
         </is>
       </c>
     </row>
@@ -8193,12 +8193,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61998</t>
+          <t>62950</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92114</t>
+          <t>90232</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61998</t>
+          <t>62950</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92114</t>
+          <t>90232</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>44,49%</t>
         </is>
       </c>
     </row>
@@ -8271,12 +8271,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44695</t>
+          <t>43629</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>70556</t>
+          <t>69254</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8306,12 +8306,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44695</t>
+          <t>43629</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>70556</t>
+          <t>69254</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,15%</t>
         </is>
       </c>
     </row>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25236</t>
+          <t>25610</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46286</t>
+          <t>45874</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8364,12 +8364,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8384,12 +8384,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25236</t>
+          <t>25610</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46286</t>
+          <t>45874</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -8509,12 +8509,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73609</t>
+          <t>72275</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>107704</t>
+          <t>105511</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8524,12 +8524,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8544,12 +8544,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>73609</t>
+          <t>72275</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>107704</t>
+          <t>105511</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,46%</t>
         </is>
       </c>
     </row>
@@ -8587,12 +8587,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>161377</t>
+          <t>163811</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>202107</t>
+          <t>201903</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8602,12 +8602,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8622,12 +8622,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>161377</t>
+          <t>163811</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>202107</t>
+          <t>201903</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8637,12 +8637,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,56%</t>
         </is>
       </c>
     </row>
@@ -8665,12 +8665,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56603</t>
+          <t>57375</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87951</t>
+          <t>87800</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56603</t>
+          <t>57375</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87951</t>
+          <t>87800</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8715,12 +8715,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -8743,12 +8743,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30486</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55492</t>
+          <t>53965</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30486</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55492</t>
+          <t>53965</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -8903,12 +8903,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61969</t>
+          <t>60571</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92776</t>
+          <t>91019</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61969</t>
+          <t>60571</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>92776</t>
+          <t>91019</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8953,12 +8953,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>96938</t>
+          <t>96410</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>129030</t>
+          <t>129583</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>96938</t>
+          <t>96410</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>129030</t>
+          <t>129583</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,6%</t>
         </is>
       </c>
     </row>
@@ -9059,12 +9059,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34926</t>
+          <t>34373</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59712</t>
+          <t>58218</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9074,12 +9074,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34926</t>
+          <t>34373</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59712</t>
+          <t>58218</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -9137,12 +9137,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17737</t>
+          <t>18022</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36864</t>
+          <t>37908</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9172,12 +9172,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17737</t>
+          <t>18022</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36864</t>
+          <t>37908</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -9297,12 +9297,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43982</t>
+          <t>42988</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71024</t>
+          <t>70249</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9312,12 +9312,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9332,12 +9332,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43982</t>
+          <t>42988</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71024</t>
+          <t>70249</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9347,12 +9347,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,03%</t>
         </is>
       </c>
     </row>
@@ -9375,12 +9375,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>88396</t>
+          <t>88873</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>120738</t>
+          <t>122079</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9410,12 +9410,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>88396</t>
+          <t>88873</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>120738</t>
+          <t>122079</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>45,23%</t>
         </is>
       </c>
     </row>
@@ -9453,12 +9453,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>56242</t>
+          <t>56638</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>86829</t>
+          <t>86047</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9468,12 +9468,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9488,12 +9488,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56242</t>
+          <t>56638</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>86829</t>
+          <t>86047</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9503,12 +9503,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,88%</t>
         </is>
       </c>
     </row>
@@ -9531,12 +9531,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28470</t>
+          <t>28094</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52739</t>
+          <t>51113</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9566,12 +9566,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28470</t>
+          <t>28094</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52739</t>
+          <t>51113</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9581,12 +9581,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -9691,12 +9691,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>10223</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24288</t>
+          <t>24196</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9706,12 +9706,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9726,12 +9726,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>10223</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24288</t>
+          <t>24196</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9741,12 +9741,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,55%</t>
         </is>
       </c>
     </row>
@@ -9769,12 +9769,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38308</t>
+          <t>38690</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56003</t>
+          <t>56808</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9784,12 +9784,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38308</t>
+          <t>38690</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>56003</t>
+          <t>56808</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9819,12 +9819,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>59,99%</t>
         </is>
       </c>
     </row>
@@ -9847,12 +9847,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15833</t>
+          <t>15135</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>31150</t>
+          <t>30847</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9862,12 +9862,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15833</t>
+          <t>15135</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>31150</t>
+          <t>30847</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9897,12 +9897,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,58%</t>
         </is>
       </c>
     </row>
@@ -9925,12 +9925,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>15068</t>
+          <t>14728</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9940,12 +9940,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>15068</t>
+          <t>14728</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -10085,12 +10085,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>10641</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>25388</t>
+          <t>24678</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10100,12 +10100,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10120,12 +10120,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>10641</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>25388</t>
+          <t>24678</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10135,12 +10135,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>39,33%</t>
         </is>
       </c>
     </row>
@@ -10163,12 +10163,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>21779</t>
+          <t>21976</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>37714</t>
+          <t>37322</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10198,12 +10198,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>21779</t>
+          <t>21976</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>37714</t>
+          <t>37322</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10213,12 +10213,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>59,49%</t>
         </is>
       </c>
     </row>
@@ -10241,12 +10241,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>17099</t>
+          <t>17960</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>17099</t>
+          <t>17960</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>28,63%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>10735</t>
+          <t>10690</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10735</t>
+          <t>10690</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -10479,12 +10479,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>85912</t>
+          <t>86335</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>122143</t>
+          <t>120946</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10494,12 +10494,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10514,12 +10514,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>85912</t>
+          <t>86335</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>122143</t>
+          <t>120946</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -10557,12 +10557,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>151903</t>
+          <t>150330</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>193582</t>
+          <t>192261</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10572,12 +10572,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10592,12 +10592,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>151903</t>
+          <t>150330</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>193582</t>
+          <t>192261</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10607,12 +10607,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>45,76%</t>
         </is>
       </c>
     </row>
@@ -10635,12 +10635,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>75620</t>
+          <t>75090</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>110366</t>
+          <t>110810</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10650,12 +10650,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10670,12 +10670,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>75620</t>
+          <t>75090</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>110366</t>
+          <t>110810</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10685,12 +10685,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,37%</t>
         </is>
       </c>
     </row>
@@ -10713,12 +10713,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>41559</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>69862</t>
+          <t>70022</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10728,12 +10728,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>41559</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>69862</t>
+          <t>70022</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -10873,12 +10873,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>117910</t>
+          <t>119307</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>160576</t>
+          <t>162575</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -10888,12 +10888,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>117910</t>
+          <t>119307</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>160576</t>
+          <t>162575</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -10923,12 +10923,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -10951,12 +10951,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>183308</t>
+          <t>183390</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>228838</t>
+          <t>228211</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10966,12 +10966,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>183308</t>
+          <t>183390</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>228838</t>
+          <t>228211</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11001,12 +11001,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,0%</t>
         </is>
       </c>
     </row>
@@ -11029,12 +11029,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>105424</t>
+          <t>105620</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>145526</t>
+          <t>146924</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11064,12 +11064,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>105424</t>
+          <t>105620</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>145526</t>
+          <t>146924</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11079,12 +11079,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>27,04%</t>
         </is>
       </c>
     </row>
@@ -11107,12 +11107,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>59282</t>
+          <t>58441</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>93594</t>
+          <t>93134</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11142,12 +11142,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>59282</t>
+          <t>58441</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>93594</t>
+          <t>93134</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -11267,12 +11267,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>491110</t>
+          <t>491489</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>573159</t>
+          <t>571532</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11302,12 +11302,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>491110</t>
+          <t>491489</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>573159</t>
+          <t>571532</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11317,12 +11317,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -11345,12 +11345,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>885927</t>
+          <t>885668</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>978449</t>
+          <t>977905</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -11360,12 +11360,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>885927</t>
+          <t>885668</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>978449</t>
+          <t>977905</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>454403</t>
+          <t>458077</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>534084</t>
+          <t>537375</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>454403</t>
+          <t>458077</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>534084</t>
+          <t>537375</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>250943</t>
+          <t>251512</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>315189</t>
+          <t>311983</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>250943</t>
+          <t>251512</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>315189</t>
+          <t>311983</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -11831,32 +11831,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>60362</t>
+          <t>66601</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51527</t>
+          <t>57912</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69939</t>
+          <t>78111</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11866,32 +11866,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>60362</t>
+          <t>66601</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51527</t>
+          <t>57912</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>69939</t>
+          <t>78111</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>42,81%</t>
         </is>
       </c>
     </row>
@@ -11909,32 +11909,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>63610</t>
+          <t>71727</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54254</t>
+          <t>61884</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74537</t>
+          <t>81905</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11944,32 +11944,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>63610</t>
+          <t>71727</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54254</t>
+          <t>61884</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74537</t>
+          <t>81905</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,89%</t>
         </is>
       </c>
     </row>
@@ -11987,32 +11987,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18868</t>
+          <t>19020</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13196</t>
+          <t>13210</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26359</t>
+          <t>26823</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -12022,32 +12022,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18868</t>
+          <t>19020</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13196</t>
+          <t>13210</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26359</t>
+          <t>26823</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -12065,32 +12065,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26114</t>
+          <t>25107</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19714</t>
+          <t>18256</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34846</t>
+          <t>32687</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12100,32 +12100,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26114</t>
+          <t>25107</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19714</t>
+          <t>18256</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34846</t>
+          <t>32687</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -12143,17 +12143,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>168954</t>
+          <t>182454</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>168954</t>
+          <t>182454</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>168954</t>
+          <t>182454</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12178,17 +12178,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>168954</t>
+          <t>182454</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>168954</t>
+          <t>182454</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>168954</t>
+          <t>182454</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12225,32 +12225,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>94042</t>
+          <t>96526</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82122</t>
+          <t>83200</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>108108</t>
+          <t>109829</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12260,32 +12260,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>94042</t>
+          <t>96526</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>82122</t>
+          <t>83200</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>108108</t>
+          <t>109829</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>45,43%</t>
         </is>
       </c>
     </row>
@@ -12303,32 +12303,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>77527</t>
+          <t>80709</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65874</t>
+          <t>68776</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91611</t>
+          <t>93914</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12338,32 +12338,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>77527</t>
+          <t>80709</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65874</t>
+          <t>68776</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91611</t>
+          <t>93914</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -12381,32 +12381,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34965</t>
+          <t>36743</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26019</t>
+          <t>27298</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46630</t>
+          <t>47478</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12416,32 +12416,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>34965</t>
+          <t>36743</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26019</t>
+          <t>27298</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46630</t>
+          <t>47478</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -12459,32 +12459,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26250</t>
+          <t>27764</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18896</t>
+          <t>19583</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37484</t>
+          <t>36995</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12494,32 +12494,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26250</t>
+          <t>27764</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18896</t>
+          <t>19583</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37484</t>
+          <t>36995</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -12537,17 +12537,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>232783</t>
+          <t>241742</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>232783</t>
+          <t>241742</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>232783</t>
+          <t>241742</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12572,17 +12572,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>232783</t>
+          <t>241742</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>232783</t>
+          <t>241742</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>232783</t>
+          <t>241742</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12619,32 +12619,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>57878</t>
+          <t>61495</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49214</t>
+          <t>52194</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67491</t>
+          <t>70992</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12654,32 +12654,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>57878</t>
+          <t>61495</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49214</t>
+          <t>52194</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67491</t>
+          <t>70992</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>44,22%</t>
         </is>
       </c>
     </row>
@@ -12697,32 +12697,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44701</t>
+          <t>45483</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35637</t>
+          <t>37123</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54599</t>
+          <t>56472</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12732,32 +12732,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44701</t>
+          <t>45483</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>35637</t>
+          <t>37123</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>54599</t>
+          <t>56472</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,18%</t>
         </is>
       </c>
     </row>
@@ -12775,32 +12775,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>26637</t>
+          <t>27098</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19457</t>
+          <t>19611</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35791</t>
+          <t>35362</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12810,32 +12810,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>26637</t>
+          <t>27098</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19457</t>
+          <t>19611</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35791</t>
+          <t>35362</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,03%</t>
         </is>
       </c>
     </row>
@@ -12853,32 +12853,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26507</t>
+          <t>26453</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18502</t>
+          <t>18938</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35249</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12888,32 +12888,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>26507</t>
+          <t>26453</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18502</t>
+          <t>18938</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35249</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,03%</t>
         </is>
       </c>
     </row>
@@ -12931,17 +12931,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>155723</t>
+          <t>160528</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>155723</t>
+          <t>160528</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>155723</t>
+          <t>160528</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12966,17 +12966,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>155723</t>
+          <t>160528</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>155723</t>
+          <t>160528</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>155723</t>
+          <t>160528</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>173814</t>
+          <t>79198</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>116570</t>
+          <t>69130</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>232335</t>
+          <t>93250</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13048,32 +13048,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>173814</t>
+          <t>79198</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>116570</t>
+          <t>69130</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>232335</t>
+          <t>93250</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>44,7%</t>
         </is>
       </c>
     </row>
@@ -13091,32 +13091,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>58051</t>
+          <t>64827</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26855</t>
+          <t>53953</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>86345</t>
+          <t>77363</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>58051</t>
+          <t>64827</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26855</t>
+          <t>53953</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>86345</t>
+          <t>77363</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>37,09%</t>
         </is>
       </c>
     </row>
@@ -13169,32 +13169,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>31931</t>
+          <t>36425</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14418</t>
+          <t>26517</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>51112</t>
+          <t>47917</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -13204,32 +13204,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>31931</t>
+          <t>36425</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14418</t>
+          <t>26517</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>51112</t>
+          <t>47917</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>22,97%</t>
         </is>
       </c>
     </row>
@@ -13247,32 +13247,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>25227</t>
+          <t>28151</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11361</t>
+          <t>19148</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41012</t>
+          <t>37808</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13282,32 +13282,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>25227</t>
+          <t>28151</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11361</t>
+          <t>19148</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41012</t>
+          <t>37808</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>18,12%</t>
         </is>
       </c>
     </row>
@@ -13325,17 +13325,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>289023</t>
+          <t>208601</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>289023</t>
+          <t>208601</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>289023</t>
+          <t>208601</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13360,17 +13360,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>289023</t>
+          <t>208601</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>289023</t>
+          <t>208601</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>289023</t>
+          <t>208601</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13407,32 +13407,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13929</t>
+          <t>14328</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>10681</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17961</t>
+          <t>18765</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13442,32 +13442,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>13929</t>
+          <t>14328</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>10681</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17961</t>
+          <t>18765</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>29,02%</t>
         </is>
       </c>
     </row>
@@ -13485,32 +13485,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>24838</t>
+          <t>28043</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20184</t>
+          <t>22904</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29709</t>
+          <t>32850</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13520,32 +13520,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>24838</t>
+          <t>28043</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20184</t>
+          <t>22904</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29709</t>
+          <t>32850</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,8%</t>
         </is>
       </c>
     </row>
@@ -13563,32 +13563,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>15309</t>
+          <t>16672</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11273</t>
+          <t>12588</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19784</t>
+          <t>21747</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13598,32 +13598,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>15309</t>
+          <t>16672</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11273</t>
+          <t>12588</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19784</t>
+          <t>21747</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -13641,32 +13641,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>9504</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -13676,32 +13676,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>9504</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -13719,17 +13719,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>59403</t>
+          <t>64661</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>59403</t>
+          <t>64661</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>59403</t>
+          <t>64661</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13754,17 +13754,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>59403</t>
+          <t>64661</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>59403</t>
+          <t>64661</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>59403</t>
+          <t>64661</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13801,32 +13801,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>20740</t>
+          <t>22081</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>17044</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26624</t>
+          <t>28376</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13836,32 +13836,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>20740</t>
+          <t>22081</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>17044</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>26624</t>
+          <t>28376</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,91%</t>
         </is>
       </c>
     </row>
@@ -13879,32 +13879,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>30707</t>
+          <t>31940</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>23994</t>
+          <t>25165</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>37537</t>
+          <t>39060</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13914,32 +13914,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>30707</t>
+          <t>31940</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>23994</t>
+          <t>25165</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>37537</t>
+          <t>39060</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,93%</t>
         </is>
       </c>
     </row>
@@ -13957,32 +13957,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>25686</t>
+          <t>25957</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19960</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>32496</t>
+          <t>33159</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13992,32 +13992,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>25686</t>
+          <t>25957</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>19960</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>32496</t>
+          <t>33159</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,29%</t>
         </is>
       </c>
     </row>
@@ -14035,32 +14035,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>8970</t>
+          <t>8942</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>13496</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14070,32 +14070,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>8970</t>
+          <t>8942</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>13496</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>16,22%</t>
         </is>
       </c>
     </row>
@@ -14113,17 +14113,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>86104</t>
+          <t>88920</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>86104</t>
+          <t>88920</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>86104</t>
+          <t>88920</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14148,17 +14148,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>86104</t>
+          <t>88920</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>86104</t>
+          <t>88920</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>86104</t>
+          <t>88920</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -14195,32 +14195,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>72590</t>
+          <t>86308</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>60308</t>
+          <t>73244</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>84792</t>
+          <t>101238</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14230,32 +14230,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>72590</t>
+          <t>86308</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>60308</t>
+          <t>73244</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>84792</t>
+          <t>101238</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,87%</t>
         </is>
       </c>
     </row>
@@ -14273,32 +14273,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>94557</t>
+          <t>109625</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>81573</t>
+          <t>94492</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>107692</t>
+          <t>124751</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14308,32 +14308,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>94557</t>
+          <t>109625</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>81573</t>
+          <t>94492</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>107692</t>
+          <t>124751</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>31,88%</t>
         </is>
       </c>
     </row>
@@ -14351,32 +14351,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>96004</t>
+          <t>110537</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>81451</t>
+          <t>95547</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>111223</t>
+          <t>126598</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14386,32 +14386,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>96004</t>
+          <t>110537</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>81451</t>
+          <t>95547</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>111223</t>
+          <t>126598</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>32,35%</t>
         </is>
       </c>
     </row>
@@ -14429,32 +14429,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>70724</t>
+          <t>84857</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>58725</t>
+          <t>71906</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>86331</t>
+          <t>102365</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14464,32 +14464,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>70724</t>
+          <t>84857</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>58725</t>
+          <t>71906</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>86331</t>
+          <t>102365</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -14507,17 +14507,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>333875</t>
+          <t>391327</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>333875</t>
+          <t>391327</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>333875</t>
+          <t>391327</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14542,17 +14542,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>333875</t>
+          <t>391327</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>333875</t>
+          <t>391327</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>333875</t>
+          <t>391327</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14589,32 +14589,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>45668</t>
+          <t>51983</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>37066</t>
+          <t>41941</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>56859</t>
+          <t>62144</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -14624,32 +14624,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>45668</t>
+          <t>51983</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>37066</t>
+          <t>41941</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>56859</t>
+          <t>62144</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,35%</t>
         </is>
       </c>
     </row>
@@ -14667,32 +14667,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>104426</t>
+          <t>113577</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>91904</t>
+          <t>98920</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>118922</t>
+          <t>126583</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14702,32 +14702,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>104426</t>
+          <t>113577</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>91904</t>
+          <t>98920</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>118922</t>
+          <t>126583</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>47,57%</t>
         </is>
       </c>
     </row>
@@ -14745,32 +14745,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>68989</t>
+          <t>77657</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>58365</t>
+          <t>65797</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>81508</t>
+          <t>91354</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14780,32 +14780,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>68989</t>
+          <t>77657</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>58365</t>
+          <t>65797</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>81508</t>
+          <t>91354</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,33%</t>
         </is>
       </c>
     </row>
@@ -14823,32 +14823,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>20511</t>
+          <t>22888</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>13561</t>
+          <t>15019</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>28255</t>
+          <t>32307</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -14858,32 +14858,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>20511</t>
+          <t>22888</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>13561</t>
+          <t>15019</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>28255</t>
+          <t>32307</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -14901,17 +14901,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>239593</t>
+          <t>266105</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>239593</t>
+          <t>266105</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>239593</t>
+          <t>266105</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -14936,17 +14936,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>239593</t>
+          <t>266105</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>239593</t>
+          <t>266105</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>239593</t>
+          <t>266105</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -14983,32 +14983,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>539022</t>
+          <t>478520</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>466406</t>
+          <t>449858</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>677370</t>
+          <t>513326</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15018,32 +15018,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>539022</t>
+          <t>478520</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>466406</t>
+          <t>449858</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>677370</t>
+          <t>513326</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>32,0%</t>
         </is>
       </c>
     </row>
@@ -15061,32 +15061,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>498418</t>
+          <t>545931</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>433308</t>
+          <t>515344</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>541739</t>
+          <t>578355</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -15096,32 +15096,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>498418</t>
+          <t>545931</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>433308</t>
+          <t>515344</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>541739</t>
+          <t>578355</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>36,05%</t>
         </is>
       </c>
     </row>
@@ -15139,32 +15139,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>318388</t>
+          <t>350108</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>271802</t>
+          <t>324297</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>351039</t>
+          <t>379849</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -15174,32 +15174,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>318388</t>
+          <t>350108</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>271802</t>
+          <t>324297</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>351039</t>
+          <t>379849</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -15217,32 +15217,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>209630</t>
+          <t>229778</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>176144</t>
+          <t>204682</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>237727</t>
+          <t>255878</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -15252,32 +15252,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>209630</t>
+          <t>229778</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>176144</t>
+          <t>204682</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>237727</t>
+          <t>255878</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -15295,17 +15295,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1565458</t>
+          <t>1604338</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1565458</t>
+          <t>1604338</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1565458</t>
+          <t>1604338</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -15330,17 +15330,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>1565458</t>
+          <t>1604338</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1565458</t>
+          <t>1604338</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1565458</t>
+          <t>1604338</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
